--- a/plan_achats.xlsx
+++ b/plan_achats.xlsx
@@ -448,10 +448,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>140238610.8522394</v>
+        <v>88323988.85151194</v>
       </c>
       <c r="D2" t="n">
-        <v>17938.70600034301</v>
+        <v>19094.23665172742</v>
       </c>
     </row>
     <row r="3">
@@ -462,10 +462,10 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>280531811.3490217</v>
+        <v>60259115.44860467</v>
       </c>
       <c r="D3" t="n">
-        <v>19842.40523300119</v>
+        <v>21868.53107010999</v>
       </c>
     </row>
     <row r="4">
@@ -476,10 +476,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>333129776.1019914</v>
+        <v>54792693.00016224</v>
       </c>
       <c r="D4" t="n">
-        <v>21154.32897615496</v>
+        <v>20559.9416843155</v>
       </c>
     </row>
     <row r="5">
@@ -490,10 +490,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>100998003.2373413</v>
+        <v>61684461.7735424</v>
       </c>
       <c r="D5" t="n">
-        <v>21851.36090055056</v>
+        <v>22934.1951992516</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>189160267.0264778</v>
+        <v>93896671.38366842</v>
       </c>
       <c r="D6" t="n">
-        <v>21177.22331319202</v>
+        <v>18555.61766631727</v>
       </c>
     </row>
     <row r="7">
@@ -518,10 +518,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>110369854.5165589</v>
+        <v>146940739.6567338</v>
       </c>
       <c r="D7" t="n">
-        <v>16509.92813223546</v>
+        <v>17367.36277025216</v>
       </c>
     </row>
     <row r="8">
@@ -532,10 +532,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>89152869.04248059</v>
+        <v>62887792.73756737</v>
       </c>
       <c r="D8" t="n">
-        <v>16742.85940883956</v>
+        <v>17498.48085940463</v>
       </c>
     </row>
     <row r="9">
@@ -546,10 +546,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>48677211.48568889</v>
+        <v>54586192.5085169</v>
       </c>
       <c r="D9" t="n">
-        <v>16655.19519903213</v>
+        <v>15377.8274182646</v>
       </c>
     </row>
     <row r="10">
@@ -560,10 +560,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>128200043.5014026</v>
+        <v>40428486.39134926</v>
       </c>
       <c r="D10" t="n">
-        <v>20551.58296476693</v>
+        <v>16139.90317150509</v>
       </c>
     </row>
     <row r="11">
@@ -574,10 +574,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>108491943.8931227</v>
+        <v>106943890.3399388</v>
       </c>
       <c r="D11" t="n">
-        <v>21486.0302577267</v>
+        <v>22852.29698916383</v>
       </c>
     </row>
     <row r="12">
@@ -588,10 +588,10 @@
         <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>77761649.55695117</v>
+        <v>46323994.91789083</v>
       </c>
       <c r="D12" t="n">
-        <v>19711.38999561746</v>
+        <v>17433.41382490664</v>
       </c>
     </row>
     <row r="13">
@@ -602,10 +602,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>71472038.06585231</v>
+        <v>165980787.0249848</v>
       </c>
       <c r="D13" t="n">
-        <v>16636.67015901563</v>
+        <v>12274.02953167058</v>
       </c>
     </row>
   </sheetData>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27317.33769633935</v>
+        <v>3259.973914755762</v>
       </c>
       <c r="C2" t="n">
-        <v>229557422.9039103</v>
+        <v>27394734.39630198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,14 +690,14 @@
         <v>2845</v>
       </c>
       <c r="F2" t="n">
-        <v>24472.33769633935</v>
+        <v>414.9739147557616</v>
       </c>
       <c r="G2" t="n">
-        <v>10.41463129249686</v>
+        <v>87.27063695579136</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🔴 Rupture risque</t>
+          <t>🟢 Suffisant</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14786.5576179267</v>
+        <v>5021.296454518822</v>
       </c>
       <c r="C3" t="n">
-        <v>32234695.60708022</v>
+        <v>10946426.27085103</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         <v>102</v>
       </c>
       <c r="F3" t="n">
-        <v>14684.5576179267</v>
+        <v>4919.296454518822</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6898157274708671</v>
+        <v>2.031347898374074</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -746,17 +746,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2141.27661493189</v>
+        <v>3402.549984559887</v>
       </c>
       <c r="C4" t="n">
-        <v>5434174.618906449</v>
+        <v>8635059.401815772</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2141.27661493189</v>
+        <v>3402.549984559887</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12664.22519507423</v>
+        <v>212.4683417730712</v>
       </c>
       <c r="C5" t="n">
-        <v>17951412.57176577</v>
+        <v>301171.7497799107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -791,18 +791,18 @@
         <v>351</v>
       </c>
       <c r="F5" t="n">
-        <v>12313.22519507423</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.771586848728195</v>
+        <v>100</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>🔴 Rupture risque</t>
+          <t>🟢 Suffisant</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>138.5316582269288</v>
       </c>
     </row>
     <row r="6">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6144.821607741679</v>
+        <v>15533.44175419113</v>
       </c>
       <c r="C6" t="n">
-        <v>12289643.21548336</v>
+        <v>31066883.50838225</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         <v>746</v>
       </c>
       <c r="F6" t="n">
-        <v>5398.821607741679</v>
+        <v>14787.44175419113</v>
       </c>
       <c r="G6" t="n">
-        <v>12.14030361858083</v>
+        <v>4.802541586115127</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -847,17 +847,17 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8502.395019553189</v>
+        <v>5764.83335155337</v>
       </c>
       <c r="C7" t="n">
-        <v>12537206.57608215</v>
+        <v>8500535.018533021</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>8502.395019553189</v>
+        <v>5764.83335155337</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -878,17 +878,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8016.061837138767</v>
+        <v>4452.833477328912</v>
       </c>
       <c r="C8" t="n">
-        <v>1684014.270746112</v>
+        <v>935451.2569172578</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>8016.061837138767</v>
+        <v>4452.833477328912</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -909,17 +909,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6218.985320814631</v>
+        <v>4167.069857182474</v>
       </c>
       <c r="C9" t="n">
-        <v>8667897.360445017</v>
+        <v>5807978.625543788</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>6218.985320814631</v>
+        <v>4167.069857182474</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5393.992804989071</v>
+        <v>15666.39102659603</v>
       </c>
       <c r="C10" t="n">
-        <v>11219505.03437727</v>
+        <v>32586093.33531974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -954,14 +954,14 @@
         <v>5082</v>
       </c>
       <c r="F10" t="n">
-        <v>311.9928049890714</v>
+        <v>10584.39102659603</v>
       </c>
       <c r="G10" t="n">
-        <v>94.21592100196166</v>
+        <v>32.43886860332127</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>🟢 Suffisant</t>
+          <t>🟡 Stock faible</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -975,17 +975,17 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8576.079694005777</v>
+        <v>18774.13054767769</v>
       </c>
       <c r="C11" t="n">
-        <v>22272422.00852076</v>
+        <v>48757167.99754088</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>8576.079694005777</v>
+        <v>18774.13054767769</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35189.20374033855</v>
+        <v>44469.1358004769</v>
       </c>
       <c r="C12" t="n">
-        <v>84806684.7982907</v>
+        <v>107171506.6618653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>28793.79625966145</v>
+        <v>19513.8641995231</v>
       </c>
     </row>
     <row r="13">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46830.06921535893</v>
+        <v>45523.67105266306</v>
       </c>
       <c r="C13" t="n">
-        <v>155926803.3615355</v>
+        <v>151576980.8470785</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
         <v>30721</v>
       </c>
       <c r="F13" t="n">
-        <v>16109.06921535893</v>
+        <v>14802.67105266306</v>
       </c>
       <c r="G13" t="n">
-        <v>65.6010134401518</v>
+        <v>67.48357346766056</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2402.635537973068</v>
+        <v>3296.154921178306</v>
       </c>
       <c r="C14" t="n">
-        <v>5485649.40758935</v>
+        <v>7525714.992935885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1090,10 +1090,10 @@
         <v>165</v>
       </c>
       <c r="F14" t="n">
-        <v>2237.635537973068</v>
+        <v>3131.154921178306</v>
       </c>
       <c r="G14" t="n">
-        <v>6.867458563407361</v>
+        <v>5.00583267308977</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1800.165251994655</v>
+        <v>3990.218903857665</v>
       </c>
       <c r="C15" t="n">
-        <v>7140139.452206559</v>
+        <v>15826724.45588297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1125,18 +1125,18 @@
         <v>2501</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1489.218903857665</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>62.67826553530891</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>🟢 Suffisant</t>
+          <t>🟡 Stock faible</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>700.8347480053453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3332.345372810765</v>
+        <v>4302.464257895419</v>
       </c>
       <c r="C16" t="n">
-        <v>9829019.264735175</v>
+        <v>12690462.52580317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         <v>1869</v>
       </c>
       <c r="F16" t="n">
-        <v>1463.345372810765</v>
+        <v>2433.464257895419</v>
       </c>
       <c r="G16" t="n">
-        <v>56.08662341093225</v>
+        <v>43.44022141660358</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18065.57639569865</v>
+        <v>17031.15582875786</v>
       </c>
       <c r="C17" t="n">
-        <v>60117360.53925828</v>
+        <v>56675088.1860324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         <v>4004</v>
       </c>
       <c r="F17" t="n">
-        <v>14061.57639569865</v>
+        <v>13027.15582875786</v>
       </c>
       <c r="G17" t="n">
-        <v>22.16369913861889</v>
+        <v>23.50985476416738</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12175.72851435086</v>
+        <v>11110.47157489996</v>
       </c>
       <c r="C18" t="n">
-        <v>20258829.40317296</v>
+        <v>18486380.33932879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
         <v>2000</v>
       </c>
       <c r="F18" t="n">
-        <v>10175.72851435086</v>
+        <v>9110.471574899955</v>
       </c>
       <c r="G18" t="n">
-        <v>16.42612183445706</v>
+        <v>18.00103610829866</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1251,17 +1251,17 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2880.02428186431</v>
+        <v>10589.48773382799</v>
       </c>
       <c r="C19" t="n">
-        <v>9296718.381857993</v>
+        <v>34182866.40479673</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2880.02428186431</v>
+        <v>10589.48773382799</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2986.789367282593</v>
+        <v>3395.793176090025</v>
       </c>
       <c r="C20" t="n">
-        <v>4894332.264591294</v>
+        <v>5564550.445931681</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>2900</v>
       </c>
       <c r="F20" t="n">
-        <v>86.78936728259305</v>
+        <v>495.7931760900246</v>
       </c>
       <c r="G20" t="n">
-        <v>97.09422538350755</v>
+        <v>85.39978289664597</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1317,17 +1317,17 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4833.40945428793</v>
+        <v>1992.294877104968</v>
       </c>
       <c r="C21" t="n">
-        <v>966580147.5885733</v>
+        <v>398417037.6138304</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>4833.40945428793</v>
+        <v>1992.294877104968</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>186152.3629822082</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -1423,18 +1423,18 @@
         <v>414</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>185738.3629822082</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>0.2223984661637461</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🟢 Suffisant</t>
+          <t>🔴 Rupture risque</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1349705.40193542</v>
+        <v>3696860.438547782</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -1458,10 +1458,10 @@
         <v>17584</v>
       </c>
       <c r="F3" t="n">
-        <v>1332121.40193542</v>
+        <v>3679276.438547782</v>
       </c>
       <c r="G3" t="n">
-        <v>1.302802817176644</v>
+        <v>0.475646843917847</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3671139.404481676</v>
+        <v>1229824.113629705</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -1493,10 +1493,10 @@
         <v>16880</v>
       </c>
       <c r="F4" t="n">
-        <v>3654259.404481676</v>
+        <v>1212944.113629705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4598027516850254</v>
+        <v>1.372553994748106</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>535319.1537329723</v>
+        <v>850637.4961399718</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -1528,10 +1528,10 @@
         <v>15760</v>
       </c>
       <c r="F5" t="n">
-        <v>519559.1537329723</v>
+        <v>834877.4961399718</v>
       </c>
       <c r="G5" t="n">
-        <v>2.944038129422396</v>
+        <v>1.852728109390408</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>97341.75515659027</v>
+        <v>3302330.000297961</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -1563,10 +1563,10 @@
         <v>7692</v>
       </c>
       <c r="F6" t="n">
-        <v>89649.75515659027</v>
+        <v>3294638.000297961</v>
       </c>
       <c r="G6" t="n">
-        <v>7.902055996038031</v>
+        <v>0.232926448880214</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1783824.576353202</v>
+        <v>3905019.153916961</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -1598,10 +1598,10 @@
         <v>15275</v>
       </c>
       <c r="F7" t="n">
-        <v>1768549.576353202</v>
+        <v>3889744.153916961</v>
       </c>
       <c r="G7" t="n">
-        <v>0.856306175085207</v>
+        <v>0.3911632542103741</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2924807.89030532</v>
+        <v>2709648.412381636</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -1633,10 +1633,10 @@
         <v>2235</v>
       </c>
       <c r="F8" t="n">
-        <v>2922572.89030532</v>
+        <v>2707413.412381636</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07641527525305906</v>
+        <v>0.08248302583417289</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>338032.7811192867</v>
+        <v>562130.2435738418</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -1668,10 +1668,10 @@
         <v>5700</v>
       </c>
       <c r="F9" t="n">
-        <v>332332.7811192867</v>
+        <v>556430.2435738418</v>
       </c>
       <c r="G9" t="n">
-        <v>1.686226992875154</v>
+        <v>1.013999880839225</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>599045.0506277765</v>
+        <v>2202613.448636221</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -1703,10 +1703,10 @@
         <v>3406</v>
       </c>
       <c r="F10" t="n">
-        <v>595639.0506277765</v>
+        <v>2199207.448636221</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5685715951464152</v>
+        <v>0.1546344866871158</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30156177.57115191</v>
+        <v>27710600.21058524</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -1773,10 +1773,10 @@
         <v>87486</v>
       </c>
       <c r="F12" t="n">
-        <v>30068691.57115191</v>
+        <v>27623114.21058524</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2901097123253814</v>
+        <v>0.3157131182116402</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2125598.754888297</v>
+        <v>1441208.337888342</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -1808,10 +1808,10 @@
         <v>2409</v>
       </c>
       <c r="F13" t="n">
-        <v>2123189.754888297</v>
+        <v>1438799.337888342</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1133327724463499</v>
+        <v>0.1671514059882325</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4222927.333455605</v>
+        <v>3780845.703583481</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -1843,10 +1843,10 @@
         <v>2966</v>
       </c>
       <c r="F14" t="n">
-        <v>4219961.333455605</v>
+        <v>3777879.703583481</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07023563906729444</v>
+        <v>0.07844805719495054</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36017.58742227611</v>
+        <v>205754.1680773602</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -1878,10 +1878,10 @@
         <v>7820</v>
       </c>
       <c r="F15" t="n">
-        <v>28197.58742227611</v>
+        <v>197934.1680773602</v>
       </c>
       <c r="G15" t="n">
-        <v>21.71161524040196</v>
+        <v>3.80065204660146</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5122301.68115088</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -1913,18 +1913,18 @@
         <v>3946</v>
       </c>
       <c r="F16" t="n">
-        <v>5118355.68115088</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07703568133287714</v>
+        <v>100</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>🔴 Rupture risque</t>
+          <t>🟢 Suffisant</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="17">
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1554746.330203658</v>
+        <v>1041767.464295619</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -1948,10 +1948,10 @@
         <v>3472</v>
       </c>
       <c r="F17" t="n">
-        <v>1551274.330203658</v>
+        <v>1038295.464295619</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2233161727125735</v>
+        <v>0.3332797499437709</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51014370.11731913</v>
+        <v>34589000.10932022</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -1983,10 +1983,10 @@
         <v>144759</v>
       </c>
       <c r="F18" t="n">
-        <v>50869611.11731913</v>
+        <v>34444241.10932022</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2837612219205957</v>
+        <v>0.418511664235688</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37313911.92488779</v>
+        <v>25002419.14309485</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -2018,10 +2018,10 @@
         <v>131575</v>
       </c>
       <c r="F19" t="n">
-        <v>37182336.92488779</v>
+        <v>24870844.14309485</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3526164725501256</v>
+        <v>0.526249077127156</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3594270.303766659</v>
+        <v>13215680.69181733</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -2053,10 +2053,10 @@
         <v>15870</v>
       </c>
       <c r="F20" t="n">
-        <v>3578400.303766659</v>
+        <v>13199810.69181733</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4415360743283231</v>
+        <v>0.1200846204601942</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>432211.0490673134</v>
+        <v>2469050.016928323</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -2088,14 +2088,14 @@
         <v>140540</v>
       </c>
       <c r="F21" t="n">
-        <v>291671.0490673134</v>
+        <v>2328510.016928323</v>
       </c>
       <c r="G21" t="n">
-        <v>32.51652180185519</v>
+        <v>5.692067760330022</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>🟡 Stock faible</t>
+          <t>🔴 Rupture risque</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>122935240.3476211</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -2123,18 +2123,18 @@
         <v>141950</v>
       </c>
       <c r="F22" t="n">
-        <v>122793290.3476211</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1154672977403479</v>
+        <v>100</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>🔴 Rupture risque</t>
+          <t>🟢 Suffisant</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>141950</v>
       </c>
     </row>
     <row r="23">
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>50675128.00146727</v>
+        <v>45370148.44300178</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -2158,10 +2158,10 @@
         <v>260691</v>
       </c>
       <c r="F23" t="n">
-        <v>50414437.00146727</v>
+        <v>45109457.44300178</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5144357997328627</v>
+        <v>0.5745870554677696</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>45926725.99748773</v>
+        <v>199395019.7035418</v>
       </c>
       <c r="C24" t="n">
         <v>2</v>
@@ -2193,10 +2193,10 @@
         <v>165499</v>
       </c>
       <c r="F24" t="n">
-        <v>45761226.99748773</v>
+        <v>199229520.7035418</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3603544481029479</v>
+        <v>0.08300056854281616</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>70195389.36732768</v>
+        <v>65031561.89715925</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -2228,10 +2228,10 @@
         <v>339923</v>
       </c>
       <c r="F25" t="n">
-        <v>69855466.36732768</v>
+        <v>64691638.89715925</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4842526027189709</v>
+        <v>0.5227046530691565</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>241249420.5692153</v>
+        <v>221684801.6846819</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -2298,10 +2298,10 @@
         <v>922001</v>
       </c>
       <c r="F27" t="n">
-        <v>240327419.5692153</v>
+        <v>220762800.6846819</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3821774982193065</v>
+        <v>0.4159062745814337</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2028196.68671572</v>
+        <v>3372781.461443051</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -2333,10 +2333,10 @@
         <v>2880</v>
       </c>
       <c r="F28" t="n">
-        <v>2025316.68671572</v>
+        <v>3369901.461443051</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1419980625579077</v>
+        <v>0.08538946364961893</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>211263522.389828</v>
+        <v>59591419.25241506</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
@@ -2368,10 +2368,10 @@
         <v>1806264</v>
       </c>
       <c r="F29" t="n">
-        <v>209457258.389828</v>
+        <v>57785155.25241506</v>
       </c>
       <c r="G29" t="n">
-        <v>0.854981484530511</v>
+        <v>3.031080686883955</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>51102131.68849763</v>
+        <v>47809450.8693647</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
@@ -2403,10 +2403,10 @@
         <v>163462</v>
       </c>
       <c r="F30" t="n">
-        <v>50938669.68849763</v>
+        <v>47645988.8693647</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3198731532305002</v>
+        <v>0.341903111262763</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>116122115.3648154</v>
+        <v>264426581.6007011</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
@@ -2438,10 +2438,10 @@
         <v>3375264</v>
       </c>
       <c r="F31" t="n">
-        <v>112746851.3648154</v>
+        <v>261051317.6007011</v>
       </c>
       <c r="G31" t="n">
-        <v>2.906650459644221</v>
+        <v>1.276446558272586</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>241249420.5692153</v>
+        <v>221684801.6846819</v>
       </c>
       <c r="C32" t="n">
         <v>2</v>
@@ -2473,10 +2473,10 @@
         <v>23658496</v>
       </c>
       <c r="F32" t="n">
-        <v>217590924.5692153</v>
+        <v>198026305.6846819</v>
       </c>
       <c r="G32" t="n">
-        <v>9.806654019802007</v>
+        <v>10.67213260458476</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>51014370.11731913</v>
+        <v>34589000.10932022</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -2508,10 +2508,10 @@
         <v>145240</v>
       </c>
       <c r="F33" t="n">
-        <v>50869130.11731913</v>
+        <v>34443760.10932022</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2847040935053939</v>
+        <v>0.4199022797448955</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>37313911.92488779</v>
+        <v>25002419.14309485</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -2543,10 +2543,10 @@
         <v>134767</v>
       </c>
       <c r="F34" t="n">
-        <v>37179144.92488779</v>
+        <v>24867652.14309485</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3611709227145185</v>
+        <v>0.5390158417419375</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>50675128.00146727</v>
+        <v>45370148.44300178</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -2578,10 +2578,10 @@
         <v>255043</v>
       </c>
       <c r="F35" t="n">
-        <v>50420085.00146727</v>
+        <v>45115105.44300178</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5032902926118221</v>
+        <v>0.5621383415141541</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3594270.303766659</v>
+        <v>13215680.69181733</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -2613,10 +2613,10 @@
         <v>18497</v>
       </c>
       <c r="F36" t="n">
-        <v>3575773.303766659</v>
+        <v>13197183.69181733</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5146246229899806</v>
+        <v>0.1399625220322755</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>432211.0490673134</v>
+        <v>2469050.016928323</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -2648,14 +2648,14 @@
         <v>123167</v>
       </c>
       <c r="F37" t="n">
-        <v>309044.0490673134</v>
+        <v>2345883.016928323</v>
       </c>
       <c r="G37" t="n">
-        <v>28.49695773992528</v>
+        <v>4.988436813978709</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>🟡 Stock faible</t>
+          <t>🔴 Rupture risque</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>122935240.3476211</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -2683,18 +2683,18 @@
         <v>141074</v>
       </c>
       <c r="F38" t="n">
-        <v>122794166.3476211</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1147547274492557</v>
+        <v>100</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>🔴 Rupture risque</t>
+          <t>🟢 Suffisant</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>141074</v>
       </c>
     </row>
     <row r="39">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3114936.165010889</v>
+        <v>105674560.0095348</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -2718,10 +2718,10 @@
         <v>188567</v>
       </c>
       <c r="F39" t="n">
-        <v>2926369.165010889</v>
+        <v>105485993.0095348</v>
       </c>
       <c r="G39" t="n">
-        <v>6.053639304654606</v>
+        <v>0.1784412444991359</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>241249420.5692153</v>
+        <v>221684801.6846819</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -2788,10 +2788,10 @@
         <v>1150248</v>
       </c>
       <c r="F41" t="n">
-        <v>240099172.5692153</v>
+        <v>220534553.6846819</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4767878808935792</v>
+        <v>0.5188664226229093</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>42811789.83247684</v>
+        <v>93720459.69400705</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -2823,10 +2823,10 @@
         <v>11000</v>
       </c>
       <c r="F42" t="n">
-        <v>42800789.83247684</v>
+        <v>93709459.69400705</v>
       </c>
       <c r="G42" t="n">
-        <v>0.02569385686289492</v>
+        <v>0.01173703163206251</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>70195389.36732768</v>
+        <v>65031561.89715925</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -2858,10 +2858,10 @@
         <v>327062</v>
       </c>
       <c r="F43" t="n">
-        <v>69868327.36732768</v>
+        <v>64704499.89715925</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4659308865551082</v>
+        <v>0.5029281020763656</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>381798.4980660943</v>
+        <v>127901.7078174894</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -2893,10 +2893,10 @@
         <v>3351.384</v>
       </c>
       <c r="F44" t="n">
-        <v>378447.1140660943</v>
+        <v>124550.3238174893</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8777886809339495</v>
+        <v>2.620280883803594</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53531.91537329724</v>
+        <v>85063.74961399718</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -2928,10 +2928,10 @@
         <v>8335.440000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>45196.47537329724</v>
+        <v>76728.30961399717</v>
       </c>
       <c r="G45" t="n">
-        <v>15.57097283344709</v>
+        <v>9.799050756432221</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>427434.7847661468</v>
+        <v>455019.0793519439</v>
       </c>
       <c r="C46" t="n">
         <v>16</v>
@@ -2963,10 +2963,10 @@
         <v>3309.373</v>
       </c>
       <c r="F46" t="n">
-        <v>424125.4117661468</v>
+        <v>451709.7063519438</v>
       </c>
       <c r="G46" t="n">
-        <v>0.7742404497590401</v>
+        <v>0.7273042274871946</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>96654.41529215356</v>
+        <v>274968.3892981865</v>
       </c>
       <c r="C47" t="n">
         <v>3</v>
@@ -2998,14 +2998,14 @@
         <v>30299</v>
       </c>
       <c r="F47" t="n">
-        <v>66355.41529215356</v>
+        <v>244669.3892981865</v>
       </c>
       <c r="G47" t="n">
-        <v>31.34776606781634</v>
+        <v>11.01908480365086</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🟡 Stock faible</t>
+          <t>🔴 Rupture risque</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1322711.293896711</v>
+        <v>3622923.229776826</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -3033,10 +3033,10 @@
         <v>98530</v>
       </c>
       <c r="F48" t="n">
-        <v>1224181.293896711</v>
+        <v>3524393.229776826</v>
       </c>
       <c r="G48" t="n">
-        <v>7.449093423080281</v>
+        <v>2.719627045645941</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5799.264917529214</v>
+        <v>5328.9615789587</v>
       </c>
       <c r="C49" t="n">
         <v>2</v>
@@ -3068,10 +3068,10 @@
         <v>2214</v>
       </c>
       <c r="F49" t="n">
-        <v>3585.264917529214</v>
+        <v>3114.9615789587</v>
       </c>
       <c r="G49" t="n">
-        <v>38.1772523153379</v>
+        <v>41.54655587576265</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9670.685265687323</v>
+        <v>10655.18188419245</v>
       </c>
       <c r="C50" t="n">
         <v>3</v>
@@ -3103,10 +3103,10 @@
         <v>863.511</v>
       </c>
       <c r="F50" t="n">
-        <v>8807.174265687323</v>
+        <v>9791.670884192452</v>
       </c>
       <c r="G50" t="n">
-        <v>8.929160408764764</v>
+        <v>8.104141340666047</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>159029.0761826113</v>
+        <v>137893.9469910551</v>
       </c>
       <c r="C51" t="n">
         <v>4</v>
@@ -3138,10 +3138,10 @@
         <v>8045</v>
       </c>
       <c r="F51" t="n">
-        <v>150984.0761826113</v>
+        <v>129848.9469910551</v>
       </c>
       <c r="G51" t="n">
-        <v>5.058823325340842</v>
+        <v>5.834193723181961</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>319384.0042547221</v>
+        <v>339339.1082137523</v>
       </c>
       <c r="C52" t="n">
         <v>14</v>
@@ -3173,10 +3173,10 @@
         <v>510.366</v>
       </c>
       <c r="F52" t="n">
-        <v>318873.6382547221</v>
+        <v>338828.7422137524</v>
       </c>
       <c r="G52" t="n">
-        <v>0.159796982065815</v>
+        <v>0.1503999944735272</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2028196.68671572</v>
+        <v>3372781.461443051</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -3208,10 +3208,10 @@
         <v>1711</v>
       </c>
       <c r="F53" t="n">
-        <v>2026485.68671572</v>
+        <v>3371070.461443051</v>
       </c>
       <c r="G53" t="n">
-        <v>0.08436065452659033</v>
+        <v>0.05072964316128403</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>126626.6347128404</v>
+        <v>128389.4894512719</v>
       </c>
       <c r="C54" t="n">
         <v>10</v>
@@ -3243,10 +3243,10 @@
         <v>1993.021</v>
       </c>
       <c r="F54" t="n">
-        <v>124633.6137128404</v>
+        <v>126396.4684512719</v>
       </c>
       <c r="G54" t="n">
-        <v>1.57393506075535</v>
+        <v>1.552324110422152</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>67157.53656727308</v>
+        <v>73994.31864022538</v>
       </c>
       <c r="C55" t="n">
         <v>3</v>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>67157.53656727308</v>
+        <v>73994.31864022538</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>28575.49863391282</v>
+        <v>19917.07780612569</v>
       </c>
       <c r="C56" t="n">
         <v>6</v>
@@ -3309,10 +3309,10 @@
         <v>165.018</v>
       </c>
       <c r="F56" t="n">
-        <v>28410.48063391282</v>
+        <v>19752.05980612569</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5774807366061497</v>
+        <v>0.8285251561815313</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>336516.6846571719</v>
+        <v>166436.9287815742</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
@@ -3344,10 +3344,10 @@
         <v>12000</v>
       </c>
       <c r="F57" t="n">
-        <v>324516.6846571719</v>
+        <v>154436.9287815742</v>
       </c>
       <c r="G57" t="n">
-        <v>3.565945032480354</v>
+        <v>7.209938375964847</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>899127.9233746504</v>
+        <v>1062647.717837448</v>
       </c>
       <c r="C58" t="n">
         <v>6</v>
@@ -3379,10 +3379,10 @@
         <v>17435.839</v>
       </c>
       <c r="F58" t="n">
-        <v>881692.0843746504</v>
+        <v>1045211.878837448</v>
       </c>
       <c r="G58" t="n">
-        <v>1.939194473524853</v>
+        <v>1.640792024235744</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>423403.6608760949</v>
+        <v>342788.8523199066</v>
       </c>
       <c r="C59" t="n">
         <v>10</v>
@@ -3414,10 +3414,10 @@
         <v>45827.765</v>
       </c>
       <c r="F59" t="n">
-        <v>377575.8958760949</v>
+        <v>296961.0873199066</v>
       </c>
       <c r="G59" t="n">
-        <v>10.82365818594352</v>
+        <v>13.3690943243485</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>36939.67558522269</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -3449,18 +3449,18 @@
         <v>35.97</v>
       </c>
       <c r="F60" t="n">
-        <v>36903.70558522269</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.09737497536223463</v>
+        <v>100</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>🔴 Rupture risque</t>
+          <t>🟢 Suffisant</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>35.97</v>
       </c>
     </row>
     <row r="61">
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22220.18124748712</v>
+        <v>73396.30393568431</v>
       </c>
       <c r="C61" t="n">
         <v>2</v>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>22220.18124748712</v>
+        <v>73396.30393568431</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>140979.980544699</v>
+        <v>138073.0950797893</v>
       </c>
       <c r="C62" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
         <v>2304.661</v>
       </c>
       <c r="F62" t="n">
-        <v>138675.319544699</v>
+        <v>135768.4340797894</v>
       </c>
       <c r="G62" t="n">
-        <v>1.634743451584805</v>
+        <v>1.669160091376374</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>67296.64274751674</v>
+        <v>68644.99963306278</v>
       </c>
       <c r="C63" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
         <v>6749.405</v>
       </c>
       <c r="F63" t="n">
-        <v>60547.23774751675</v>
+        <v>61895.59463306278</v>
       </c>
       <c r="G63" t="n">
-        <v>10.02933389310725</v>
+        <v>9.832333070257834</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>64468.59912535717</v>
+        <v>62667.21209410816</v>
       </c>
       <c r="C64" t="n">
         <v>4</v>
@@ -3585,10 +3585,10 @@
         <v>21.566</v>
       </c>
       <c r="F64" t="n">
-        <v>64447.03312535717</v>
+        <v>62645.64609410816</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0334519445010207</v>
+        <v>0.03441353026462077</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5966.11100248442</v>
+        <v>6043.055664271789</v>
       </c>
       <c r="C65" t="n">
         <v>14</v>
@@ -3620,10 +3620,10 @@
         <v>72.96599999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>5893.14500248442</v>
+        <v>5970.089664271789</v>
       </c>
       <c r="G65" t="n">
-        <v>1.223007751106464</v>
+        <v>1.207435510339498</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>60124755.91856745</v>
+        <v>59532909.39764674</v>
       </c>
       <c r="C66" t="n">
         <v>10</v>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>999937524685.6584</v>
+        <v>999938116532.1793</v>
       </c>
     </row>
     <row r="67">
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>805791.4297030568</v>
+        <v>855315.9218247612</v>
       </c>
       <c r="C67" t="n">
         <v>10</v>
@@ -3690,10 +3690,10 @@
         <v>4562.478</v>
       </c>
       <c r="F67" t="n">
-        <v>801228.9517030568</v>
+        <v>850753.4438247612</v>
       </c>
       <c r="G67" t="n">
-        <v>0.5662107875336083</v>
+        <v>0.5334260573878069</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1547.246379008572</v>
+        <v>1504.013090258596</v>
       </c>
       <c r="C68" t="n">
         <v>4</v>
@@ -3725,10 +3725,10 @@
         <v>32.392</v>
       </c>
       <c r="F68" t="n">
-        <v>1514.854379008572</v>
+        <v>1471.621090258596</v>
       </c>
       <c r="G68" t="n">
-        <v>2.093525662070433</v>
+        <v>2.15370465920816</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>10860833.54152406</v>
+        <v>8914093.142867811</v>
       </c>
       <c r="C69" t="n">
         <v>6</v>
@@ -3760,10 +3760,10 @@
         <v>167638.353</v>
       </c>
       <c r="F69" t="n">
-        <v>10693195.18852406</v>
+        <v>8746454.789867811</v>
       </c>
       <c r="G69" t="n">
-        <v>1.543512773297471</v>
+        <v>1.880599072875157</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>264435358.525274</v>
+        <v>279426957.9071108</v>
       </c>
       <c r="C70" t="n">
         <v>9</v>
@@ -3795,10 +3795,10 @@
         <v>2118947.862</v>
       </c>
       <c r="F70" t="n">
-        <v>262316410.663274</v>
+        <v>277308010.0451108</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8013103367935105</v>
+        <v>0.7583190533478866</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>21618480.81411977</v>
+        <v>30805943.17963546</v>
       </c>
       <c r="C71" t="n">
         <v>9</v>
@@ -3830,10 +3830,10 @@
         <v>78044.53999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>21540436.27411978</v>
+        <v>30727898.63963546</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3610084384330393</v>
+        <v>0.2533424785759912</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>870552879.5435467</v>
+        <v>974079849.8574128</v>
       </c>
       <c r="C72" t="n">
         <v>14</v>
@@ -3865,10 +3865,10 @@
         <v>3124631.623</v>
       </c>
       <c r="F72" t="n">
-        <v>867428247.9205467</v>
+        <v>970955218.2344128</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3589249655504356</v>
+        <v>0.3207777702677443</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>44840848.23056815</v>
+        <v>22177720.76014476</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>44840848.23056815</v>
+        <v>22177720.76014476</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>63160424.1093673</v>
+        <v>52716157.7715826</v>
       </c>
       <c r="C74" t="n">
         <v>7</v>
@@ -3931,10 +3931,10 @@
         <v>148420</v>
       </c>
       <c r="F74" t="n">
-        <v>63012004.1093673</v>
+        <v>52567737.7715826</v>
       </c>
       <c r="G74" t="n">
-        <v>0.2349889224033692</v>
+        <v>0.2815455569487804</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>8612007.499115175</v>
+        <v>5810163.377110468</v>
       </c>
       <c r="C75" t="n">
         <v>2</v>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>8612007.499115175</v>
+        <v>5810163.377110468</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4509698.881922565</v>
+        <v>3042077.01047849</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>4509698.881922565</v>
+        <v>3042077.01047849</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>316179890.4157687</v>
+        <v>315863225.0604036</v>
       </c>
       <c r="C77" t="n">
         <v>14</v>
@@ -4028,10 +4028,10 @@
         <v>75105.23299999999</v>
       </c>
       <c r="F77" t="n">
-        <v>316104785.1827687</v>
+        <v>315788119.8274036</v>
       </c>
       <c r="G77" t="n">
-        <v>0.02375395630039548</v>
+        <v>0.02377777057954036</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>120624710.2846076</v>
+        <v>110842400.842341</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>120624710.2846076</v>
+        <v>110842400.842341</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>120624710.2846076</v>
+        <v>110842400.842341</v>
       </c>
       <c r="C79" t="n">
         <v>2</v>
@@ -4094,10 +4094,10 @@
         <v>17241</v>
       </c>
       <c r="F79" t="n">
-        <v>120607469.2846076</v>
+        <v>110825159.842341</v>
       </c>
       <c r="G79" t="n">
-        <v>0.01429309132376009</v>
+        <v>0.01555451692581353</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
